--- a/sample_templates/期末存货.xlsx
+++ b/sample_templates/期末存货.xlsx
@@ -672,7 +672,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. 单价/金额可留空，系统按月末加权价自动计算。</t>
+          <t>5. 单价/金额可留空，系统按月末加权价自动回填。</t>
         </is>
       </c>
     </row>
